--- a/data/info_search_data.xlsx
+++ b/data/info_search_data.xlsx
@@ -1,28 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\블랙\Downloads\최종본\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GEUMSAN\Desktop\새 폴더 (6)\guide333-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9722AB90-0AD3-4A11-B19E-46D3A582ADDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="390" windowWidth="24660" windowHeight="18900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="390" windowWidth="24660" windowHeight="18900"/>
   </bookViews>
   <sheets>
     <sheet name="던전목록" sheetId="1" r:id="rId1"/>
     <sheet name="드랍목록" sheetId="2" r:id="rId2"/>
-    <sheet name="공략영상" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="133">
   <si>
     <t>던전ID</t>
   </si>
@@ -39,12 +37,6 @@
     <t>아이템</t>
   </si>
   <si>
-    <t>영상제목</t>
-  </si>
-  <si>
-    <t>영상링크</t>
-  </si>
-  <si>
     <t>ice</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -121,18 +113,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>BDH</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GAC</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ARL</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>입문</t>
   </si>
   <si>
@@ -175,15 +155,6 @@
     <t>RTP</t>
   </si>
   <si>
-    <t>BDH</t>
-  </si>
-  <si>
-    <t>GAC</t>
-  </si>
-  <si>
-    <t>ARL</t>
-  </si>
-  <si>
     <t>호천조각</t>
   </si>
   <si>
@@ -340,9 +311,6 @@
     <t>돌풍목걸이</t>
   </si>
   <si>
-    <t>삼섬석류석</t>
-  </si>
-  <si>
     <t>공허조각</t>
   </si>
   <si>
@@ -359,18 +327,160 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>bu</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>BU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성석류석상자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ba</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ba</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Up</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대정기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 대정기 드랍정보</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화천장갑 : 설영의 대정기(제0 격납고)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금강허리띠 : 삼도천의 대정기(삼도천)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>극X팔찌 : 제천의 대정기(선도원)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌운 목걸이 : 설영의 대정기(제0 격납고)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설풍 귀걸이 : 삼도천의 대정기(삼도천)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설풍 반지 : 신아만의 대정기 (나류성지)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Upa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌파재료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 돌파재료 드랍정보</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>무신의 회랑 : 사가령</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6단</t>
+  </si>
+  <si>
+    <t>6단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>섭무팔찌 : 뒤틀린 천무궁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천음 목걸이 : 천명 부화장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>섭무허리띠 : 뒤틀린 천무궁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설영장갑 : 제0 격납고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아얀카반지 : 번개구름골짜기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아얀카귀걸이 : 번개구름골짜기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9단</t>
+  </si>
+  <si>
+    <t>9단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여명팔찌 : 법기 연구소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대풍귀걸이 : 법기 연구소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌풍 목걸이 : 그루족 고도시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강풍장갑 : 그루족 고도시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장풍허리띠 : 흑룡교 비밀전당</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>열풍 반지 : 흑룡교 비밀전당</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -752,8 +862,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -774,100 +884,122 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -878,8 +1010,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C159"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C171"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" style="4" customWidth="1"/>
@@ -901,1814 +1033,1877 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B153" s="5"/>
+      <c r="A153" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B154" s="5"/>
+      <c r="A154" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B155" s="5"/>
+      <c r="A155" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B156" s="5"/>
+      <c r="A156" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B157" s="5"/>
+      <c r="A157" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B158" s="5"/>
+      <c r="A158" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B159" s="5"/>
+      <c r="A159" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>132</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>